--- a/artfynd/A 64567-2023 artfynd.xlsx
+++ b/artfynd/A 64567-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 64567-2023 artfynd.xlsx
+++ b/artfynd/A 64567-2023 artfynd.xlsx
@@ -815,12 +815,7 @@
         <v>97112317</v>
       </c>
       <c r="B3" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -852,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624476.5431584482</v>
+        <v>624477</v>
       </c>
       <c r="R3" t="n">
-        <v>6703323.72229171</v>
+        <v>6703324</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -885,19 +880,9 @@
           <t>2002-05-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2002-05-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 64567-2023 artfynd.xlsx
+++ b/artfynd/A 64567-2023 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>97112317</v>
       </c>
       <c r="B3" t="n">
-        <v>106181</v>
+        <v>106190</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 64567-2023 artfynd.xlsx
+++ b/artfynd/A 64567-2023 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>97112317</v>
       </c>
       <c r="B3" t="n">
-        <v>106190</v>
+        <v>106202</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 64567-2023 artfynd.xlsx
+++ b/artfynd/A 64567-2023 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>97112317</v>
       </c>
       <c r="B3" t="n">
-        <v>106202</v>
+        <v>106211</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 64567-2023 artfynd.xlsx
+++ b/artfynd/A 64567-2023 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>97112317</v>
       </c>
       <c r="B3" t="n">
-        <v>106211</v>
+        <v>106216</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 64567-2023 artfynd.xlsx
+++ b/artfynd/A 64567-2023 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>97112317</v>
       </c>
       <c r="B3" t="n">
-        <v>106216</v>
+        <v>106244</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 64567-2023 artfynd.xlsx
+++ b/artfynd/A 64567-2023 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>97112317</v>
       </c>
       <c r="B3" t="n">
-        <v>106244</v>
+        <v>106250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 64567-2023 artfynd.xlsx
+++ b/artfynd/A 64567-2023 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>97112317</v>
       </c>
       <c r="B3" t="n">
-        <v>106250</v>
+        <v>106257</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 64567-2023 artfynd.xlsx
+++ b/artfynd/A 64567-2023 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>97112317</v>
       </c>
       <c r="B3" t="n">
-        <v>106257</v>
+        <v>106261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 64567-2023 artfynd.xlsx
+++ b/artfynd/A 64567-2023 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>97112317</v>
       </c>
       <c r="B3" t="n">
-        <v>106261</v>
+        <v>106268</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 64567-2023 artfynd.xlsx
+++ b/artfynd/A 64567-2023 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>97112317</v>
       </c>
       <c r="B3" t="n">
-        <v>106271</v>
+        <v>106276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 64567-2023 artfynd.xlsx
+++ b/artfynd/A 64567-2023 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>97112317</v>
       </c>
       <c r="B3" t="n">
-        <v>106276</v>
+        <v>106284</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 64567-2023 artfynd.xlsx
+++ b/artfynd/A 64567-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>75659839</v>
+        <v>80687183</v>
       </c>
       <c r="B2" t="n">
-        <v>43464</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87412</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101735</v>
+        <v>3624</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stortyllen, N om Rämsön, Gstr</t>
+          <t>Sågtyllen, N om Rämsön, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624538.9704951452</v>
+        <v>624452</v>
       </c>
       <c r="R2" t="n">
-        <v>6703450.319602913</v>
+        <v>6703380</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,27 +745,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2009-05-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2009-05-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-18</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Gamla kläckhål i fnöskticka på björklåga, omkr. 92 cm, i en 15-20 årig granplantering.</t>
+          <t>2 ex. vid vägkant, under gran.  Gulbrun, trådig hatt. Sporer ellipsoida, 7-8 x 4-5 μm, vårtiga.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,17 +769,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Granplantering med kvarlämnade, äldre lövträd.</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>Fnöskticka på björk.</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Fnöskticka på björk.</t>
+          <t>Vägkant, i äldre barrskog med inslag av lövträd.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -812,48 +787,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97112317</v>
+        <v>75659839</v>
       </c>
       <c r="B3" t="n">
-        <v>106284</v>
+        <v>44177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220785</v>
+        <v>101735</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rämsön, O Kågbosjön, Gstr</t>
+          <t>Stortyllen, N om Rämsön, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624477</v>
+        <v>624539</v>
       </c>
       <c r="R3" t="n">
-        <v>6703324</v>
+        <v>6703450</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,12 +857,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2002-05-16</t>
+          <t>2009-05-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2002-05-16</t>
+          <t>2009-05-07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gamla kläckhål i fnöskticka på björklåga, omkr. 92 cm, i en 15-20 årig granplantering.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,26 +881,264 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>skog, Lövskog, bård mellan bäck och hygge som är 12-15 år och planterat med gran, något fuktigt</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>Gst Fyndnr 231064N</t>
+          <t>Granplantering med kvarlämnade, äldre lövträd.</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Fnöskticka på björk.</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Fnöskticka på björk.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>75953623</v>
+      </c>
+      <c r="B4" t="n">
+        <v>43378</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>201075</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Brunfläckig pärlemorfjäril</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Boloria selene</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sågtyllen, N om Rämsön, Gstr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>624655</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6703373</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2009-06-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2009-06-16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2 imago i kraftledningsgata.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Kraftledningsgata.</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>97112317</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rämsön, O Kågbosjön, Gstr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>624477</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6703324</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2002-05-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2002-05-16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>skog, Lövskog, bård mellan bäck och hygge som är 12-15 år och planterat med gran, något fuktigt</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 231064N</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Magnus Bergström</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Birgitta Hellström</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Gästriklands flora (2016)</t>
         </is>

--- a/artfynd/A 64567-2023 artfynd.xlsx
+++ b/artfynd/A 64567-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80687183</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75659839</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1032,6 +1047,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75953623</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1143,8 +1163,19 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97112317</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>